--- a/data/nzd0352/nzd0352.xlsx
+++ b/data/nzd0352/nzd0352.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H460"/>
+  <dimension ref="A1:H462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14236,6 +14236,66 @@
         <v>430.7</v>
       </c>
       <c r="H460" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:06:43+00:00</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>236.72</v>
+      </c>
+      <c r="C461" t="n">
+        <v>294.25</v>
+      </c>
+      <c r="D461" t="n">
+        <v>333.91</v>
+      </c>
+      <c r="E461" t="n">
+        <v>323.99</v>
+      </c>
+      <c r="F461" t="n">
+        <v>319.48</v>
+      </c>
+      <c r="G461" t="n">
+        <v>430.61</v>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:00+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>236.72</v>
+      </c>
+      <c r="C462" t="n">
+        <v>294.25</v>
+      </c>
+      <c r="D462" t="n">
+        <v>333.35</v>
+      </c>
+      <c r="E462" t="n">
+        <v>324.45</v>
+      </c>
+      <c r="F462" t="n">
+        <v>318.95</v>
+      </c>
+      <c r="G462" t="n">
+        <v>430.56</v>
+      </c>
+      <c r="H462" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14252,7 +14312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B471"/>
+  <dimension ref="A1:B473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18965,6 +19025,26 @@
       </c>
       <c r="B471" t="n">
         <v>-0.26</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B472" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B473" t="n">
+        <v>-0.24</v>
       </c>
     </row>
   </sheetData>
@@ -19133,28 +19213,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.180693789008922</v>
+        <v>1.129295817372239</v>
       </c>
       <c r="J2" t="n">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="K2" t="n">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03914814397419297</v>
+        <v>0.03598548380170241</v>
       </c>
       <c r="M2" t="n">
-        <v>37.82688162869228</v>
+        <v>37.95532037500189</v>
       </c>
       <c r="N2" t="n">
-        <v>1967.093226714284</v>
+        <v>1974.421015570687</v>
       </c>
       <c r="O2" t="n">
-        <v>44.35192472389765</v>
+        <v>44.43445752533372</v>
       </c>
       <c r="P2" t="n">
-        <v>265.8888546644168</v>
+        <v>266.4268811249145</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19211,28 +19291,28 @@
         <v>0.1532</v>
       </c>
       <c r="I3" t="n">
-        <v>0.040587660313373</v>
+        <v>0.0003795181639556511</v>
       </c>
       <c r="J3" t="n">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="K3" t="n">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005825164362587287</v>
+        <v>4.852549106981741e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>7.89743743188968</v>
+        <v>8.145326236045481</v>
       </c>
       <c r="N3" t="n">
-        <v>163.6268829264671</v>
+        <v>172.7337560271171</v>
       </c>
       <c r="O3" t="n">
-        <v>12.79167240537636</v>
+        <v>13.14282146371612</v>
       </c>
       <c r="P3" t="n">
-        <v>341.063316092873</v>
+        <v>341.4820325475896</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19289,28 +19369,28 @@
         <v>0.0784</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04270874267115492</v>
+        <v>-0.05011774979708326</v>
       </c>
       <c r="J4" t="n">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="K4" t="n">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005227429182104171</v>
+        <v>0.007134516354013631</v>
       </c>
       <c r="M4" t="n">
-        <v>3.611407175262625</v>
+        <v>3.631971766464645</v>
       </c>
       <c r="N4" t="n">
-        <v>20.09541968115577</v>
+        <v>20.34187808815875</v>
       </c>
       <c r="O4" t="n">
-        <v>4.482791505430045</v>
+        <v>4.510197122982404</v>
       </c>
       <c r="P4" t="n">
-        <v>343.6010873105233</v>
+        <v>343.6782438433528</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19367,28 +19447,28 @@
         <v>0.0551</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2429201866225966</v>
+        <v>0.2314010396724863</v>
       </c>
       <c r="J5" t="n">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="K5" t="n">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06844907974928471</v>
+        <v>0.06205650479413927</v>
       </c>
       <c r="M5" t="n">
-        <v>5.651182329783865</v>
+        <v>5.692112804883962</v>
       </c>
       <c r="N5" t="n">
-        <v>46.4936949823116</v>
+        <v>47.09795182175432</v>
       </c>
       <c r="O5" t="n">
-        <v>6.81862852649355</v>
+        <v>6.862794752996357</v>
       </c>
       <c r="P5" t="n">
-        <v>331.4191665655731</v>
+        <v>331.5391228086213</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19445,28 +19525,28 @@
         <v>0.092</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07654238490004159</v>
+        <v>0.0673181720637261</v>
       </c>
       <c r="J6" t="n">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="K6" t="n">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006976808492220599</v>
+        <v>0.005398880942438899</v>
       </c>
       <c r="M6" t="n">
-        <v>5.763507898397606</v>
+        <v>5.784885250788318</v>
       </c>
       <c r="N6" t="n">
-        <v>48.27635067261274</v>
+        <v>48.58384329933448</v>
       </c>
       <c r="O6" t="n">
-        <v>6.948118498745739</v>
+        <v>6.970211137356922</v>
       </c>
       <c r="P6" t="n">
-        <v>328.1499468156578</v>
+        <v>328.246006334515</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19523,28 +19603,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03146458926432984</v>
+        <v>-0.03190319506436323</v>
       </c>
       <c r="J7" t="n">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="K7" t="n">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01336436767629923</v>
+        <v>0.0138604070304309</v>
       </c>
       <c r="M7" t="n">
-        <v>1.591022715090007</v>
+        <v>1.586494694121848</v>
       </c>
       <c r="N7" t="n">
-        <v>4.231363922699986</v>
+        <v>4.214177411855753</v>
       </c>
       <c r="O7" t="n">
-        <v>2.057027934350913</v>
+        <v>2.052846173451814</v>
       </c>
       <c r="P7" t="n">
-        <v>431.9482820918092</v>
+        <v>431.9528497183921</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19582,7 +19662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H460"/>
+  <dimension ref="A1:H462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38901,6 +38981,90 @@
         </is>
       </c>
     </row>
+    <row r="461">
+      <c r="A461" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:06:43+00:00</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>-41.38579283166532,174.06009346284532</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>-41.38609981682844,174.05895628286456</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>-41.38646721312715,174.05797016125317</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>-41.38658654433365,174.05702256970054</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>-41.38692705941924,174.05611993355993</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>-41.38807378295555,174.05666228338242</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:00+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>-41.38579283166532,174.06009346284532</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>-41.38609981682844,174.05895628286456</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>-41.38646223806379,174.05796905944482</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>-41.38659034068875,174.0570247728754</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>-41.386923545776455,174.05611564291146</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>-41.388073528330565,174.05666179015898</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0352/nzd0352.xlsx
+++ b/data/nzd0352/nzd0352.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H462"/>
+  <dimension ref="A1:H464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14296,6 +14296,66 @@
         <v>430.56</v>
       </c>
       <c r="H462" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>236.72</v>
+      </c>
+      <c r="C463" t="n">
+        <v>294.25</v>
+      </c>
+      <c r="D463" t="n">
+        <v>333.44</v>
+      </c>
+      <c r="E463" t="n">
+        <v>324.18</v>
+      </c>
+      <c r="F463" t="n">
+        <v>319.45</v>
+      </c>
+      <c r="G463" t="n">
+        <v>430.01</v>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:07+00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>224.77</v>
+      </c>
+      <c r="C464" t="n">
+        <v>292.69</v>
+      </c>
+      <c r="D464" t="n">
+        <v>333.91</v>
+      </c>
+      <c r="E464" t="n">
+        <v>325.29</v>
+      </c>
+      <c r="F464" t="n">
+        <v>319.16</v>
+      </c>
+      <c r="G464" t="n">
+        <v>430.05</v>
+      </c>
+      <c r="H464" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14312,7 +14372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B473"/>
+  <dimension ref="A1:B475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19045,6 +19105,26 @@
       </c>
       <c r="B473" t="n">
         <v>-0.24</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B474" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B475" t="n">
+        <v>0.14</v>
       </c>
     </row>
   </sheetData>
@@ -19213,28 +19293,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.129295817372239</v>
+        <v>1.0739294371894</v>
       </c>
       <c r="J2" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K2" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03598548380170241</v>
+        <v>0.03265558347364117</v>
       </c>
       <c r="M2" t="n">
-        <v>37.95532037500189</v>
+        <v>38.10638489643026</v>
       </c>
       <c r="N2" t="n">
-        <v>1974.421015570687</v>
+        <v>1984.665467433834</v>
       </c>
       <c r="O2" t="n">
-        <v>44.43445752533372</v>
+        <v>44.54958436881127</v>
       </c>
       <c r="P2" t="n">
-        <v>266.4268811249145</v>
+        <v>267.0081829324361</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19291,28 +19371,28 @@
         <v>0.1532</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0003795181639556511</v>
+        <v>-0.03961017041067578</v>
       </c>
       <c r="J3" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K3" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L3" t="n">
-        <v>4.852549106981741e-08</v>
+        <v>0.0005045263793761467</v>
       </c>
       <c r="M3" t="n">
-        <v>8.145326236045481</v>
+        <v>8.39175041555125</v>
       </c>
       <c r="N3" t="n">
-        <v>172.7337560271171</v>
+        <v>181.8141896593861</v>
       </c>
       <c r="O3" t="n">
-        <v>13.14282146371612</v>
+        <v>13.48384921524214</v>
       </c>
       <c r="P3" t="n">
-        <v>341.4820325475896</v>
+        <v>341.8996829967591</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19369,28 +19449,28 @@
         <v>0.0784</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.05011774979708326</v>
+        <v>-0.05732395449691501</v>
       </c>
       <c r="J4" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K4" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007134516354013631</v>
+        <v>0.009256480969334291</v>
       </c>
       <c r="M4" t="n">
-        <v>3.631971766464645</v>
+        <v>3.651565998468195</v>
       </c>
       <c r="N4" t="n">
-        <v>20.34187808815875</v>
+        <v>20.57334990124529</v>
       </c>
       <c r="O4" t="n">
-        <v>4.510197122982404</v>
+        <v>4.535785477868776</v>
       </c>
       <c r="P4" t="n">
-        <v>343.6782438433528</v>
+        <v>343.7535003159533</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19447,28 +19527,28 @@
         <v>0.0551</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2314010396724863</v>
+        <v>0.2205509162590686</v>
       </c>
       <c r="J5" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K5" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06205650479413927</v>
+        <v>0.05638300361291848</v>
       </c>
       <c r="M5" t="n">
-        <v>5.692112804883962</v>
+        <v>5.729279199088102</v>
       </c>
       <c r="N5" t="n">
-        <v>47.09795182175432</v>
+        <v>47.61926409078002</v>
       </c>
       <c r="O5" t="n">
-        <v>6.862794752996357</v>
+        <v>6.900671278272863</v>
       </c>
       <c r="P5" t="n">
-        <v>331.5391228086213</v>
+        <v>331.6524314040489</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19525,28 +19605,28 @@
         <v>0.092</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0673181720637261</v>
+        <v>0.05836351347109855</v>
       </c>
       <c r="J6" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K6" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L6" t="n">
-        <v>0.005398880942438899</v>
+        <v>0.004060881500047131</v>
       </c>
       <c r="M6" t="n">
-        <v>5.784885250788318</v>
+        <v>5.804783565579793</v>
       </c>
       <c r="N6" t="n">
-        <v>48.58384329933448</v>
+        <v>48.86666839757103</v>
       </c>
       <c r="O6" t="n">
-        <v>6.970211137356922</v>
+        <v>6.990469826669094</v>
       </c>
       <c r="P6" t="n">
-        <v>328.246006334515</v>
+        <v>328.3395279800534</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19603,28 +19683,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03190319506436323</v>
+        <v>-0.03279160670717966</v>
       </c>
       <c r="J7" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K7" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0138604070304309</v>
+        <v>0.01475209510061071</v>
       </c>
       <c r="M7" t="n">
-        <v>1.586494694121848</v>
+        <v>1.5844123553879</v>
       </c>
       <c r="N7" t="n">
-        <v>4.214177411855753</v>
+        <v>4.200825189154044</v>
       </c>
       <c r="O7" t="n">
-        <v>2.052846173451814</v>
+        <v>2.049591468843009</v>
       </c>
       <c r="P7" t="n">
-        <v>431.9528497183921</v>
+        <v>431.9621277653236</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19662,7 +19742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H462"/>
+  <dimension ref="A1:H464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39065,6 +39145,90 @@
         </is>
       </c>
     </row>
+    <row r="463">
+      <c r="A463" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>-41.38579283166532,174.06009346284532</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>-41.38609981682844,174.05895628286456</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>-41.38646303762755,174.05796923652116</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>-41.386588112393376,174.0570234797075</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>-41.386926860533805,174.05611969069304</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>-41.388070727455506,174.05665636470138</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:07+00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>-41.385688874186734,174.06013048065745</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>-41.38608586558943,174.0589584971447</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>-41.38646721312715,174.05797016125317</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>-41.38659727316313,174.05702879606494</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>-41.38692493797455,174.05611734297966</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>-41.38807093115552,174.0566567592801</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0352/nzd0352.xlsx
+++ b/data/nzd0352/nzd0352.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H464"/>
+  <dimension ref="A1:H465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14131,7 +14131,7 @@
         <v>282.78</v>
       </c>
       <c r="C457" t="n">
-        <v>324.5</v>
+        <v>335.45</v>
       </c>
       <c r="D457" t="n">
         <v>340.31</v>
@@ -14161,7 +14161,7 @@
         <v>264.53</v>
       </c>
       <c r="C458" t="n">
-        <v>313.28</v>
+        <v>334.65</v>
       </c>
       <c r="D458" t="n">
         <v>339.37</v>
@@ -14191,7 +14191,7 @@
         <v>264.53</v>
       </c>
       <c r="C459" t="n">
-        <v>309.66</v>
+        <v>332.79</v>
       </c>
       <c r="D459" t="n">
         <v>338.03</v>
@@ -14221,7 +14221,7 @@
         <v>236.72</v>
       </c>
       <c r="C460" t="n">
-        <v>300.45</v>
+        <v>328.22</v>
       </c>
       <c r="D460" t="n">
         <v>335.65</v>
@@ -14251,7 +14251,7 @@
         <v>236.72</v>
       </c>
       <c r="C461" t="n">
-        <v>294.25</v>
+        <v>325.1</v>
       </c>
       <c r="D461" t="n">
         <v>333.91</v>
@@ -14281,7 +14281,7 @@
         <v>236.72</v>
       </c>
       <c r="C462" t="n">
-        <v>294.25</v>
+        <v>325.1</v>
       </c>
       <c r="D462" t="n">
         <v>333.35</v>
@@ -14311,7 +14311,7 @@
         <v>236.72</v>
       </c>
       <c r="C463" t="n">
-        <v>294.25</v>
+        <v>325.1</v>
       </c>
       <c r="D463" t="n">
         <v>333.44</v>
@@ -14341,7 +14341,7 @@
         <v>224.77</v>
       </c>
       <c r="C464" t="n">
-        <v>292.69</v>
+        <v>322.91</v>
       </c>
       <c r="D464" t="n">
         <v>333.91</v>
@@ -14356,6 +14356,36 @@
         <v>430.05</v>
       </c>
       <c r="H464" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>223.77</v>
+      </c>
+      <c r="C465" t="n">
+        <v>324.03</v>
+      </c>
+      <c r="D465" t="n">
+        <v>334.16</v>
+      </c>
+      <c r="E465" t="n">
+        <v>325.8</v>
+      </c>
+      <c r="F465" t="n">
+        <v>318.87</v>
+      </c>
+      <c r="G465" t="n">
+        <v>429.48</v>
+      </c>
+      <c r="H465" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14372,7 +14402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B475"/>
+  <dimension ref="A1:B476"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19125,6 +19155,16 @@
       </c>
       <c r="B475" t="n">
         <v>0.14</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B476" t="n">
+        <v>0.58</v>
       </c>
     </row>
   </sheetData>
@@ -19293,28 +19333,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0739294371894</v>
+        <v>1.043682300526639</v>
       </c>
       <c r="J2" t="n">
+        <v>464</v>
+      </c>
+      <c r="K2" t="n">
         <v>463</v>
       </c>
-      <c r="K2" t="n">
-        <v>462</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.03265558347364117</v>
+        <v>0.03087171181331461</v>
       </c>
       <c r="M2" t="n">
-        <v>38.10638489643026</v>
+        <v>38.19493773559208</v>
       </c>
       <c r="N2" t="n">
-        <v>1984.665467433834</v>
+        <v>1991.564237079128</v>
       </c>
       <c r="O2" t="n">
-        <v>44.54958436881127</v>
+        <v>44.62694519098443</v>
       </c>
       <c r="P2" t="n">
-        <v>267.0081829324361</v>
+        <v>267.326770063601</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19371,28 +19411,28 @@
         <v>0.1532</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.03961017041067578</v>
+        <v>0.03769186780110197</v>
       </c>
       <c r="J3" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="K3" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005045263793761467</v>
+        <v>0.0005284229637333437</v>
       </c>
       <c r="M3" t="n">
-        <v>8.39175041555125</v>
+        <v>7.827287342471895</v>
       </c>
       <c r="N3" t="n">
-        <v>181.8141896593861</v>
+        <v>157.5876227154112</v>
       </c>
       <c r="O3" t="n">
-        <v>13.48384921524214</v>
+        <v>12.55339088515176</v>
       </c>
       <c r="P3" t="n">
-        <v>341.8996829967591</v>
+        <v>341.097158458115</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19449,28 +19489,28 @@
         <v>0.0784</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.05732395449691501</v>
+        <v>-0.06067464281728367</v>
       </c>
       <c r="J4" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="K4" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009256480969334291</v>
+        <v>0.01033827479683447</v>
       </c>
       <c r="M4" t="n">
-        <v>3.651565998468195</v>
+        <v>3.660409758015388</v>
       </c>
       <c r="N4" t="n">
-        <v>20.57334990124529</v>
+        <v>20.66765385822723</v>
       </c>
       <c r="O4" t="n">
-        <v>4.535785477868776</v>
+        <v>4.546169140961127</v>
       </c>
       <c r="P4" t="n">
-        <v>343.7535003159533</v>
+        <v>343.788611286068</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19527,28 +19567,28 @@
         <v>0.0551</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2205509162590686</v>
+        <v>0.2156367284490019</v>
       </c>
       <c r="J5" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="K5" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05638300361291848</v>
+        <v>0.05395508820959927</v>
       </c>
       <c r="M5" t="n">
-        <v>5.729279199088102</v>
+        <v>5.744850925473492</v>
       </c>
       <c r="N5" t="n">
-        <v>47.61926409078002</v>
+        <v>47.81485420164689</v>
       </c>
       <c r="O5" t="n">
-        <v>6.900671278272863</v>
+        <v>6.914828573554582</v>
       </c>
       <c r="P5" t="n">
-        <v>331.6524314040489</v>
+        <v>331.7039258687203</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19605,28 +19645,28 @@
         <v>0.092</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05836351347109855</v>
+        <v>0.05376479038423036</v>
       </c>
       <c r="J6" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="K6" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004060881500047131</v>
+        <v>0.003446189339257888</v>
       </c>
       <c r="M6" t="n">
-        <v>5.804783565579793</v>
+        <v>5.815178718114715</v>
       </c>
       <c r="N6" t="n">
-        <v>48.86666839757103</v>
+        <v>49.0225110818898</v>
       </c>
       <c r="O6" t="n">
-        <v>6.990469826669094</v>
+        <v>7.001607749787887</v>
       </c>
       <c r="P6" t="n">
-        <v>328.3395279800534</v>
+        <v>328.3877167739462</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19683,28 +19723,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03279160670717966</v>
+        <v>-0.03345831919127686</v>
       </c>
       <c r="J7" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="K7" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01475209510061071</v>
+        <v>0.01540067764268516</v>
       </c>
       <c r="M7" t="n">
-        <v>1.5844123553879</v>
+        <v>1.584545535902671</v>
       </c>
       <c r="N7" t="n">
-        <v>4.200825189154044</v>
+        <v>4.197260864252945</v>
       </c>
       <c r="O7" t="n">
-        <v>2.049591468843009</v>
+        <v>2.048721763503513</v>
       </c>
       <c r="P7" t="n">
-        <v>431.9621277653236</v>
+        <v>431.9691140677983</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19742,7 +19782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H464"/>
+  <dimension ref="A1:H465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38906,7 +38946,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>-41.38637034564901,174.0589133455268</t>
+          <t>-41.38646827260451,174.0588978028382</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -38948,7 +38988,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>-41.38627000405294,174.05892927141454</t>
+          <t>-41.386461118123854,174.05889893837858</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -38990,7 +39030,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>-41.3862376300257,174.05893440970368</t>
+          <t>-41.386444483956254,174.05890157850905</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -39032,7 +39072,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>-41.38615526405975,174.05894748251168</t>
+          <t>-41.386403613984946,174.05890806527583</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -39074,7 +39114,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>-41.38609981682844,174.05895628286456</t>
+          <t>-41.38637571150967,174.05891249387378</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -39116,7 +39156,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>-41.38609981682844,174.05895628286456</t>
+          <t>-41.38637571150967,174.05891249387378</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -39158,7 +39198,7 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>-41.38609981682844,174.05895628286456</t>
+          <t>-41.38637571150967,174.05891249387378</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -39200,7 +39240,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>-41.38608586558943,174.0589584971447</t>
+          <t>-41.38635612611822,174.05891560240673</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -39224,6 +39264,48 @@
         </is>
       </c>
       <c r="H464" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>-41.38568017481558,174.06013357837713</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>-41.38636614239149,174.05891401265492</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>-41.38646943413758,174.05797065313192</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>-41.38660148216537,174.05703123871618</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>-41.38692301541527,174.05611499526646</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>-41.388068028430204,174.05665113653356</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
